--- a/sample/jarvia-customer-template.xlsx
+++ b/sample/jarvia-customer-template.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -568,8 +568,6 @@
     <col width="11" customWidth="1" min="43" max="43"/>
     <col width="26" customWidth="1" min="44" max="44"/>
     <col width="26" customWidth="1" min="45" max="45"/>
-    <col width="11" customWidth="1" min="46" max="46"/>
-    <col width="11" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -796,16 +794,6 @@
       <c r="AS1" s="3" t="inlineStr">
         <is>
           <t>기타메모</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>위도</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>경도</t>
         </is>
       </c>
     </row>
@@ -995,8 +983,6 @@
           <t>2세 승계 관심</t>
         </is>
       </c>
-      <c r="AT2" s="4" t="inlineStr"/>
-      <c r="AU2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1108,8 +1094,6 @@
         </is>
       </c>
       <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1229,8 +1213,6 @@
         </is>
       </c>
       <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="8">
@@ -1656,7 +1638,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>연락처 · 이메일 · 회사 · 직함 · 직업 · 주소 · 직장주소 · 관계 · 상태 · 소개자 · 관심항목 · 다음연락일 · 메모 · 위도 · 경도</t>
+          <t>연락처 · 이메일 · 회사 · 직함 · 직업 · 주소 · 직장주소 · 관계 · 상태 · 소개자 · 관심항목 · 다음연락일 · 메모</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1794,12 +1776,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>위도·경도</t>
+          <t>지도 좌표</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>비워두면 주소로 자동 계산됩니다. 내보내기 파일의 값을 그대로 다시 올리면 계산을 건너뛰어 훨씬 빠릅니다.</t>
+          <t>주소만 적으면 자동으로 계산됩니다. 내보내기 파일에 붙어 나오는 _위도·_경도 열을 그대로 다시 올리면 계산을 건너뛰어 훨씬 빠릅니다.</t>
         </is>
       </c>
       <c r="C19" s="6" t="n"/>

--- a/sample/jarvia-customer-template.xlsx
+++ b/sample/jarvia-customer-template.xlsx
@@ -113,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -149,11 +149,55 @@
         <color rgb="00E8DDBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E8DDBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E8DDBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E8DDBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E8DDBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E8DDBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E8DDBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E8DDBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E8DDBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -185,6 +229,8 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1244,33 +1290,35 @@
       </c>
       <c r="AS4" s="4" t="inlineStr"/>
     </row>
-    <row r="5" ht="138" customHeight="1">
+    <row r="5" ht="168" customHeight="1">
       <c r="A5" s="15" t="n"/>
       <c r="B5" s="16" t="inlineStr">
         <is>
           <t>✅ 실제 사용 시: 위 예시 3명(2~4행)과 이 안내 줄(5행)을 모두 지운 뒤 2행부터 본인 고객을 적으세요. 예시를 남겨두면 고객으로 등록됩니다.
 ① 이름은 필수입니다. 생년월일은 다시 올릴 때 같은 사람인지 판단하는 기준이니 꼭 넣으세요.
-② 연락처: 01012345678처럼 하이픈 없이 입력하면 맨 앞 0이 사라질 수 있습니다. 반드시 010-1234-5678처럼 하이픈을 넣어 입력하세요.
-③ 다른 양식(구글 시트 등)을 쓰실 분은 위 1행 전체를 복사해 그 양식의 1행에 붙여넣은 뒤 사용하세요. 열 이름이 달라도 그 파일을 그냥 올려도 됩니다.
-④ 주소는 시/도부터 적으세요 (서울 강남구 …, 경기 성남시 …). 없으면 지도에 표시되지 않을 수 있습니다.
-⑤ 관계·상태·관심항목·계약유형은 칸을 클릭하면 나오는 목록에서 고르세요.
-⑥ 이 시트(고객목록)만 읽힙니다. 시트 순서를 바꾸지 마세요.
-⑦ 저장 후 JARVIA → 고객입력 → 엑셀 파일 올리기. 엑셀이 없으면 구글 시트로 열어 작성한 뒤 .xlsx로 다운로드해 올리세요.</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="15" t="n"/>
-      <c r="L5" s="15" t="n"/>
-      <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
+② 생년월일: 연도를 반드시 4자리로 적으세요. 1975-01-01 · 19750101 · 1975년 1월 1일 — 모두 됩니다.
+　 750101처럼 6자리로 적거나 주민등록번호를 넣으면 생년월일이 등록되지 않습니다. 주민등록번호는 넣지 마세요.
+③ 연락처: 01012345678처럼 하이픈 없이 입력하면 맨 앞 0이 사라질 수 있습니다. 반드시 010-1234-5678처럼 하이픈을 넣어 입력하세요.
+④ 다른 양식(구글 시트 등)을 쓰실 분은 위 1행 전체를 복사해 그 양식의 1행에 붙여넣은 뒤 사용하세요. 열 이름이 달라도 그 파일을 그냥 올려도 됩니다.
+⑤ 주소는 시/도부터 적으세요 (서울 강남구 …, 경기 성남시 …). 없으면 지도에 표시되지 않을 수 있습니다.
+⑥ 관계·상태·관심항목·계약유형은 칸을 클릭하면 나오는 목록에서 고르세요.
+⑦ 이 시트(고객목록)만 읽힙니다. 시트 순서를 바꾸지 마세요.
+⑧ 저장 후 JARVIA → 고객입력 → 엑셀 파일 올리기. 엑셀이 없으면 구글 시트로 열어 작성한 뒤 .xlsx로 다운로드해 올리세요.</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="13" t="n"/>
@@ -16261,7 +16309,7 @@
   <mergeCells count="1">
     <mergeCell ref="B5:O5"/>
   </mergeCells>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="고객 상태" error="가망 · 신규 · 계약자 · VIP · 휴면 중에서 고르세요. &quot;기존(예전 표기)&quot;은 옛 자료용이며 새로 쓰지 마세요." promptTitle="고객 상태" prompt="가망 · 신규 · 계약자 · VIP · 휴면 중에서 고르세요. &quot;기존(예전 표기)&quot;은 옛 자료용이며 새로 쓰지 마세요." type="list" errorStyle="stop">
       <formula1>'선택목록'!$B$2:$B$7</formula1>
     </dataValidation>
@@ -16289,6 +16337,9 @@
     <dataValidation sqref="A5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="안내 줄입니다" error="이 줄(5행)은 안내용입니다. 예시와 함께 지우고 2행부터 적어주세요." type="custom" errorStyle="stop">
       <formula1>FALSE</formula1>
     </dataValidation>
+    <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="생년월일 형식" prompt="연도는 반드시 4자리로 적으세요.&#10;1975-01-01 · 19750101 · 1975년 1월 1일&#10;&#10;750101(6자리)이나 주민등록번호를 넣으면&#10;생년월일이 등록되지 않습니다." type="custom">
+      <formula1>TRUE</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17577,7 +17628,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>3. 생년월일 형식 자유: 1970-01-01 · 1970.01.01 · 19700101 모두 인식합니다.</t>
+          <t>3. 생년월일은 연도를 반드시 4자리로: 1975-01-01 · 1975.01.01 · 19750101 · 1975년 1월 1일 모두 인식합니다. 750101(6자리)·주민등록번호는 인식하지 않습니다.</t>
         </is>
       </c>
     </row>
